--- a/output/pdf_financials_xlsx/TITI.xlsx
+++ b/output/pdf_financials_xlsx/TITI.xlsx
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/output/pdf_financials_xlsx/TITI.xlsx
+++ b/output/pdf_financials_xlsx/TITI.xlsx
@@ -2692,10 +2692,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.001475</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.000577</v>
@@ -2837,7 +2835,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005069</v>
+        <v>0.003594</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.000265</v>
@@ -4813,7 +4811,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -5337,7 +5339,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.001475</v>
       </c>
